--- a/output/laminas_comunales/comunal_s_fonasa_a_2021_arica_y_parinacota.xlsx
+++ b/output/laminas_comunales/comunal_s_fonasa_a_2021_arica_y_parinacota.xlsx
@@ -384,7 +384,7 @@
         </is>
       </c>
       <c r="C2">
-        <v>202133</v>
+        <v>82.25683055661813</v>
       </c>
     </row>
   </sheetData>
@@ -440,7 +440,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Personas afiliadas a FONASA</t>
+          <t>Porcentaje de residentes afiliados a FONASA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/output/laminas_comunales/comunal_s_fonasa_a_2021_arica_y_parinacota.xlsx
+++ b/output/laminas_comunales/comunal_s_fonasa_a_2021_arica_y_parinacota.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -385,6 +385,501 @@
       </c>
       <c r="C2">
         <v>82.25683055661813</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>42.91062693807125</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>39.34620361854689</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>32.88230362912743</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>19.61185672312338</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>18.72960192728723</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>15.57985463956962</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>13.63995214337454</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>11.90352169418965</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>11.33786940350135</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>11.03306827708009</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>11.02208078654155</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>10.07227327109802</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>9.893217869729057</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>8.701278618343412</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>5.796511675226057</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>4.096706194502999</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>2.523460327020274</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>2.494974240438848</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>2.049777401580571</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>2.007048271708433</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>1.839387304972043</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>1.707944362603466</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>1.618416661918985</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>1.563886153320257</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>1.218797561590989</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>1.081250457812106</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>0.8244687344852564</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>0.6531452709026834</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>0.09563186209478541</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>0.0724360487356247</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>0.03336941570966981</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>0.002441664564122181</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
